--- a/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0003T0006Z000C1N11_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0003T0006Z000C1N11_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.81390220534626</v>
+        <v>5.169759108368768</v>
       </c>
       <c r="D2" t="n">
-        <v>31.57653259703499</v>
+        <v>5.131186547018187</v>
       </c>
       <c r="E2" t="n">
-        <v>7.287133623046069</v>
+        <v>1.184159213744986</v>
       </c>
       <c r="F2" t="n">
-        <v>7.169755888134741</v>
+        <v>1.165085331821895</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>39.45234591609147</v>
+        <v>6.411006211364864</v>
       </c>
       <c r="D3" t="n">
-        <v>39.11385967511853</v>
+        <v>6.35600219720676</v>
       </c>
       <c r="E3" t="n">
-        <v>7.287133623046069</v>
+        <v>1.184159213744986</v>
       </c>
       <c r="F3" t="n">
-        <v>7.169755888134741</v>
+        <v>1.165085331821895</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.1963212702522</v>
+        <v>4.906902206415983</v>
       </c>
       <c r="D4" t="n">
-        <v>29.84917077947568</v>
+        <v>4.850490251664799</v>
       </c>
       <c r="E4" t="n">
-        <v>7.287133623046069</v>
+        <v>1.184159213744986</v>
       </c>
       <c r="F4" t="n">
-        <v>7.169755888134741</v>
+        <v>1.165085331821895</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>39.28619481979086</v>
+        <v>6.384006658216014</v>
       </c>
       <c r="D5" t="n">
-        <v>39.25536574337792</v>
+        <v>6.378996933298912</v>
       </c>
       <c r="E5" t="n">
-        <v>7.287133623046069</v>
+        <v>1.184159213744986</v>
       </c>
       <c r="F5" t="n">
-        <v>7.169755888134741</v>
+        <v>1.165085331821895</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>31.3647146426365</v>
+        <v>5.096766129428431</v>
       </c>
       <c r="D6" t="n">
-        <v>31.02955993231301</v>
+        <v>5.042303489000865</v>
       </c>
       <c r="E6" t="n">
-        <v>7.287133623046069</v>
+        <v>1.184159213744986</v>
       </c>
       <c r="F6" t="n">
-        <v>7.169755888134741</v>
+        <v>1.165085331821895</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>38.36139109501594</v>
+        <v>6.23372605294009</v>
       </c>
       <c r="D7" t="n">
-        <v>38.13321278742961</v>
+        <v>6.196647077957311</v>
       </c>
       <c r="E7" t="n">
-        <v>7.287133623046069</v>
+        <v>1.184159213744986</v>
       </c>
       <c r="F7" t="n">
-        <v>7.169755888134741</v>
+        <v>1.165085331821895</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>34.89882842223864</v>
+        <v>5.67105961861378</v>
       </c>
       <c r="D8" t="n">
-        <v>35.01155118303631</v>
+        <v>5.689377067243401</v>
       </c>
       <c r="E8" t="n">
-        <v>7.287133623046069</v>
+        <v>1.184159213744986</v>
       </c>
       <c r="F8" t="n">
-        <v>7.169755888134741</v>
+        <v>1.165085331821895</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>17.70728040643831</v>
+        <v>2.877433066046225</v>
       </c>
       <c r="D9" t="n">
-        <v>17.98828211233283</v>
+        <v>2.923095843254085</v>
       </c>
       <c r="E9" t="n">
-        <v>7.287133623046069</v>
+        <v>1.184159213744986</v>
       </c>
       <c r="F9" t="n">
-        <v>7.169755888134741</v>
+        <v>1.165085331821895</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>14.6696496194477</v>
+        <v>2.383818063160251</v>
       </c>
       <c r="D10" t="n">
-        <v>15.01696254531689</v>
+        <v>2.440256413613995</v>
       </c>
       <c r="E10" t="n">
-        <v>7.287133623046069</v>
+        <v>1.184159213744986</v>
       </c>
       <c r="F10" t="n">
-        <v>7.169755888134741</v>
+        <v>1.165085331821895</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>23.4610901961115</v>
+        <v>3.812427156868118</v>
       </c>
       <c r="D11" t="n">
-        <v>23.4632370790343</v>
+        <v>3.812776025343073</v>
       </c>
       <c r="E11" t="n">
-        <v>7.287133623046069</v>
+        <v>1.184159213744986</v>
       </c>
       <c r="F11" t="n">
-        <v>7.169755888134741</v>
+        <v>1.165085331821895</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>28.50523677385319</v>
+        <v>4.632100975751143</v>
       </c>
       <c r="D12" t="n">
-        <v>28.82251178512503</v>
+        <v>4.683658165082818</v>
       </c>
       <c r="E12" t="n">
-        <v>7.287133623046069</v>
+        <v>1.184159213744986</v>
       </c>
       <c r="F12" t="n">
-        <v>7.169755888134741</v>
+        <v>1.165085331821895</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>25.06914237084004</v>
+        <v>4.073735635261508</v>
       </c>
       <c r="D13" t="n">
-        <v>25.2591893380842</v>
+        <v>4.104618267438682</v>
       </c>
       <c r="E13" t="n">
-        <v>7.287133623046069</v>
+        <v>1.184159213744986</v>
       </c>
       <c r="F13" t="n">
-        <v>7.169755888134741</v>
+        <v>1.165085331821895</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>29.2152078085536</v>
+        <v>4.74747126888996</v>
       </c>
       <c r="D14" t="n">
-        <v>29.55881810369598</v>
+        <v>4.803307941850598</v>
       </c>
       <c r="E14" t="n">
-        <v>7.287133623046069</v>
+        <v>1.184159213744986</v>
       </c>
       <c r="F14" t="n">
-        <v>7.169755888134741</v>
+        <v>1.165085331821895</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>27.6539636783421</v>
+        <v>4.493769097730591</v>
       </c>
       <c r="D15" t="n">
-        <v>27.94998327271595</v>
+        <v>4.541872281816342</v>
       </c>
       <c r="E15" t="n">
-        <v>7.287133623046069</v>
+        <v>1.184159213744986</v>
       </c>
       <c r="F15" t="n">
-        <v>7.169755888134741</v>
+        <v>1.165085331821895</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>38.47876260139542</v>
+        <v>6.252798922726757</v>
       </c>
       <c r="D16" t="n">
-        <v>38.62211602461601</v>
+        <v>6.276093854000102</v>
       </c>
       <c r="E16" t="n">
-        <v>7.287133623046069</v>
+        <v>1.184159213744986</v>
       </c>
       <c r="F16" t="n">
-        <v>7.169755888134741</v>
+        <v>1.165085331821895</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>36.66310340237456</v>
+        <v>5.957754302885866</v>
       </c>
       <c r="D17" t="n">
-        <v>36.96042413015089</v>
+        <v>6.00606892114952</v>
       </c>
       <c r="E17" t="n">
-        <v>7.287133623046069</v>
+        <v>1.184159213744986</v>
       </c>
       <c r="F17" t="n">
-        <v>7.169755888134741</v>
+        <v>1.165085331821895</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
